--- a/german_dictionary_curated.xlsx
+++ b/german_dictionary_curated.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sile9\Documents\projects\parldebates_analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5971C52C-A9F6-45FC-A764-AE0AEFCCF91F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F517791-6FD5-4210-A085-C8F0871C63EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="168">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="162">
   <si>
     <t>keyword_german</t>
   </si>
@@ -470,24 +470,6 @@
   </si>
   <si>
     <t>Turbines</t>
-  </si>
-  <si>
-    <t>Umwelt</t>
-  </si>
-  <si>
-    <t>Environment</t>
-  </si>
-  <si>
-    <t>Umweltanliegen</t>
-  </si>
-  <si>
-    <t>Environmental concerns</t>
-  </si>
-  <si>
-    <t>umweltfreundlichen</t>
-  </si>
-  <si>
-    <t>environmentally friendly</t>
   </si>
   <si>
     <t>Verbrennungsmotoren</t>
@@ -857,7 +839,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B89"/>
+  <dimension ref="A1:B86"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="23.44140625" bestFit="1" customWidth="1"/>
@@ -1551,30 +1533,6 @@
         <v>161</v>
       </c>
     </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A87" t="s">
-        <v>162</v>
-      </c>
-      <c r="B87" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A88" t="s">
-        <v>164</v>
-      </c>
-      <c r="B88" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A89" t="s">
-        <v>166</v>
-      </c>
-      <c r="B89" t="s">
-        <v>167</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>

--- a/german_dictionary_curated.xlsx
+++ b/german_dictionary_curated.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sile9\Documents\projects\parldebates_analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F517791-6FD5-4210-A085-C8F0871C63EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0CAC578-BB2E-4697-9452-D06EB15E7523}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="162">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="148">
   <si>
     <t>keyword_german</t>
   </si>
@@ -43,18 +43,6 @@
     <t>Nuclear power</t>
   </si>
   <si>
-    <t>Ausstoss</t>
-  </si>
-  <si>
-    <t>Output</t>
-  </si>
-  <si>
-    <t>Beimischquote</t>
-  </si>
-  <si>
-    <t>Admixture quota</t>
-  </si>
-  <si>
     <t>Benzin</t>
   </si>
   <si>
@@ -85,12 +73,6 @@
     <t>Diesel</t>
   </si>
   <si>
-    <t>elektrisch</t>
-  </si>
-  <si>
-    <t>electric</t>
-  </si>
-  <si>
     <t>Elektrizität</t>
   </si>
   <si>
@@ -118,12 +100,6 @@
     <t>Emission rights</t>
   </si>
   <si>
-    <t>Energie</t>
-  </si>
-  <si>
-    <t>Energy</t>
-  </si>
-  <si>
     <t>Energiegesetzes</t>
   </si>
   <si>
@@ -142,12 +118,6 @@
     <t>Energy crisis</t>
   </si>
   <si>
-    <t>Energien</t>
-  </si>
-  <si>
-    <t>Energies</t>
-  </si>
-  <si>
     <t>Energienachfrage</t>
   </si>
   <si>
@@ -256,12 +226,6 @@
     <t>Small hydropower plants</t>
   </si>
   <si>
-    <t>Klima</t>
-  </si>
-  <si>
-    <t>Climate</t>
-  </si>
-  <si>
     <t>Klimaeffekt</t>
   </si>
   <si>
@@ -476,12 +440,6 @@
   </si>
   <si>
     <t>Internal combustion engines</t>
-  </si>
-  <si>
-    <t>Verkehr</t>
-  </si>
-  <si>
-    <t>Traffic</t>
   </si>
   <si>
     <t>Wärme-Kraft-Koppelung</t>
@@ -839,13 +797,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B86"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:B79"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="23.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="23.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -853,7 +811,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -861,7 +819,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -869,7 +827,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -877,7 +835,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>7</v>
       </c>
@@ -885,31 +843,31 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>9</v>
       </c>
       <c r="B6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
+      <c r="B7" t="s">
         <v>11</v>
       </c>
-      <c r="B7" t="s">
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
         <v>12</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>13</v>
       </c>
       <c r="B8" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>14</v>
       </c>
@@ -917,31 +875,31 @@
         <v>15</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>16</v>
       </c>
       <c r="B10" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
+      <c r="B11" t="s">
         <v>18</v>
       </c>
-      <c r="B11" t="s">
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
         <v>19</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
-        <v>20</v>
       </c>
       <c r="B12" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>21</v>
       </c>
@@ -949,39 +907,39 @@
         <v>22</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>23</v>
       </c>
       <c r="B14" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
+      <c r="B15" t="s">
         <v>25</v>
       </c>
-      <c r="B15" t="s">
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
+      <c r="B16" t="s">
         <v>27</v>
       </c>
-      <c r="B16" t="s">
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
         <v>28</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
-        <v>29</v>
       </c>
       <c r="B17" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>30</v>
       </c>
@@ -989,7 +947,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>32</v>
       </c>
@@ -997,7 +955,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>34</v>
       </c>
@@ -1005,7 +963,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>36</v>
       </c>
@@ -1013,7 +971,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>38</v>
       </c>
@@ -1021,7 +979,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>40</v>
       </c>
@@ -1029,7 +987,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>42</v>
       </c>
@@ -1037,7 +995,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>44</v>
       </c>
@@ -1045,7 +1003,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>46</v>
       </c>
@@ -1053,7 +1011,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>48</v>
       </c>
@@ -1061,55 +1019,55 @@
         <v>49</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>50</v>
       </c>
       <c r="B28" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A29" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A29" t="s">
+      <c r="B29" t="s">
         <v>52</v>
       </c>
-      <c r="B29" t="s">
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A30" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A30" t="s">
+      <c r="B30" t="s">
         <v>54</v>
       </c>
-      <c r="B30" t="s">
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A31" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A31" t="s">
+      <c r="B31" t="s">
         <v>56</v>
       </c>
-      <c r="B31" t="s">
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A32" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A32" t="s">
+      <c r="B32" t="s">
         <v>58</v>
       </c>
-      <c r="B32" t="s">
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A33" t="s">
         <v>59</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A33" t="s">
-        <v>60</v>
       </c>
       <c r="B33" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>61</v>
       </c>
@@ -1117,7 +1075,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>63</v>
       </c>
@@ -1125,55 +1083,55 @@
         <v>64</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>65</v>
       </c>
       <c r="B36" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A37" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A37" t="s">
+      <c r="B37" t="s">
         <v>67</v>
       </c>
-      <c r="B37" t="s">
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A38" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A38" t="s">
+      <c r="B38" t="s">
         <v>69</v>
       </c>
-      <c r="B38" t="s">
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A39" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A39" t="s">
+      <c r="B39" t="s">
         <v>71</v>
       </c>
-      <c r="B39" t="s">
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A40" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A40" t="s">
+      <c r="B40" t="s">
         <v>73</v>
       </c>
-      <c r="B40" t="s">
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A41" t="s">
         <v>74</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A41" t="s">
-        <v>75</v>
       </c>
       <c r="B41" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>76</v>
       </c>
@@ -1181,7 +1139,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>78</v>
       </c>
@@ -1189,215 +1147,215 @@
         <v>79</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>80</v>
       </c>
       <c r="B44" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A45" t="s">
         <v>81</v>
       </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A45" t="s">
+      <c r="B45" t="s">
         <v>82</v>
       </c>
-      <c r="B45" t="s">
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A46" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A46" t="s">
+      <c r="B46" t="s">
         <v>84</v>
       </c>
-      <c r="B46" t="s">
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A47" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A47" t="s">
+      <c r="B47" t="s">
         <v>86</v>
       </c>
-      <c r="B47" t="s">
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A48" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A48" t="s">
+      <c r="B48" t="s">
         <v>88</v>
       </c>
-      <c r="B48" t="s">
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A49" t="s">
         <v>89</v>
       </c>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A49" t="s">
+      <c r="B49" t="s">
         <v>90</v>
       </c>
-      <c r="B49" t="s">
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A50" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A50" t="s">
+      <c r="B50" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A51" t="s">
         <v>92</v>
       </c>
-      <c r="B50" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A51" t="s">
+      <c r="B51" t="s">
         <v>93</v>
       </c>
-      <c r="B51" t="s">
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A52" t="s">
         <v>94</v>
       </c>
-    </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A52" t="s">
+      <c r="B52" t="s">
         <v>95</v>
       </c>
-      <c r="B52" t="s">
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A53" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A53" t="s">
+      <c r="B53" t="s">
         <v>97</v>
       </c>
-      <c r="B53" t="s">
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A54" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A54" t="s">
+      <c r="B54" t="s">
         <v>99</v>
       </c>
-      <c r="B54" t="s">
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A55" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A55" t="s">
+      <c r="B55" t="s">
         <v>101</v>
       </c>
-      <c r="B55" t="s">
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A56" t="s">
         <v>102</v>
       </c>
-    </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A56" t="s">
+      <c r="B56" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A57" t="s">
         <v>103</v>
       </c>
-      <c r="B56" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A57" t="s">
+      <c r="B57" t="s">
         <v>104</v>
       </c>
-      <c r="B57" t="s">
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A58" t="s">
         <v>105</v>
       </c>
-    </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A58" t="s">
+      <c r="B58" t="s">
         <v>106</v>
       </c>
-      <c r="B58" t="s">
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A59" t="s">
         <v>107</v>
       </c>
-    </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A59" t="s">
+      <c r="B59" t="s">
         <v>108</v>
       </c>
-      <c r="B59" t="s">
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A60" t="s">
         <v>109</v>
       </c>
-    </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A60" t="s">
+      <c r="B60" t="s">
         <v>110</v>
       </c>
-      <c r="B60" t="s">
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A61" t="s">
         <v>111</v>
       </c>
-    </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A61" t="s">
+      <c r="B61" t="s">
         <v>112</v>
       </c>
-      <c r="B61" t="s">
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A62" t="s">
         <v>113</v>
-      </c>
-    </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A62" t="s">
-        <v>114</v>
       </c>
       <c r="B62" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>115</v>
       </c>
       <c r="B63" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A64" t="s">
         <v>116</v>
       </c>
-    </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A64" t="s">
+      <c r="B64" t="s">
         <v>117</v>
       </c>
-      <c r="B64" t="s">
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A65" t="s">
         <v>118</v>
       </c>
-    </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A65" t="s">
+      <c r="B65" t="s">
         <v>119</v>
       </c>
-      <c r="B65" t="s">
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A66" t="s">
         <v>120</v>
       </c>
-    </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A66" t="s">
+      <c r="B66" t="s">
         <v>121</v>
       </c>
-      <c r="B66" t="s">
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A67" t="s">
         <v>122</v>
       </c>
-    </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A67" t="s">
+      <c r="B67" t="s">
         <v>123</v>
       </c>
-      <c r="B67" t="s">
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A68" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A68" t="s">
+      <c r="B68" t="s">
         <v>125</v>
       </c>
-      <c r="B68" t="s">
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A69" t="s">
         <v>126</v>
       </c>
-    </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A69" t="s">
+      <c r="B69" t="s">
         <v>127</v>
       </c>
-      <c r="B69" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.3">
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
         <v>128</v>
       </c>
@@ -1405,7 +1363,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
         <v>130</v>
       </c>
@@ -1413,7 +1371,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
         <v>132</v>
       </c>
@@ -1421,7 +1379,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
         <v>134</v>
       </c>
@@ -1429,7 +1387,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
         <v>136</v>
       </c>
@@ -1437,7 +1395,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
         <v>138</v>
       </c>
@@ -1445,7 +1403,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
         <v>140</v>
       </c>
@@ -1453,7 +1411,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
         <v>142</v>
       </c>
@@ -1461,7 +1419,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
         <v>144</v>
       </c>
@@ -1469,68 +1427,12 @@
         <v>145</v>
       </c>
     </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
         <v>146</v>
       </c>
       <c r="B79" t="s">
         <v>147</v>
-      </c>
-    </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A80" t="s">
-        <v>148</v>
-      </c>
-      <c r="B80" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A81" t="s">
-        <v>150</v>
-      </c>
-      <c r="B81" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A82" t="s">
-        <v>152</v>
-      </c>
-      <c r="B82" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A83" t="s">
-        <v>154</v>
-      </c>
-      <c r="B83" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A84" t="s">
-        <v>156</v>
-      </c>
-      <c r="B84" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A85" t="s">
-        <v>158</v>
-      </c>
-      <c r="B85" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A86" t="s">
-        <v>160</v>
-      </c>
-      <c r="B86" t="s">
-        <v>161</v>
       </c>
     </row>
   </sheetData>
